--- a/data/Framework_2_France.xlsx
+++ b/data/Framework_2_France.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://digiplace-my.sharepoint.com/personal/aurelien_brun_wavestone_com/Documents/Desktop/mapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CA2BE91-D453-4AEE-B25E-DC4735057887}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7B5D369-C003-4774-8621-053525073CA1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B5DE09A6-CED4-42BE-9EC0-2641ED5338CA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="483">
   <si>
     <t>Le dirigeant exécutif de l’entité est responsable de la sécurité numérique au sein de son entité et en particulier du suivi de la conformité des systèmes d’information aux présentes mesures.</t>
   </si>
@@ -1566,6 +1566,15 @@
   </si>
   <si>
     <t>Frande_2;154</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>Essential</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -1883,10 +1892,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4918862F-568D-4B2E-807D-414F70C16208}">
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="5" max="6" width="10.6640625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>325</v>
       </c>
@@ -1899,8 +1911,14 @@
       <c r="D1" s="1" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>328</v>
       </c>
@@ -1913,8 +1931,14 @@
       <c r="D2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>329</v>
       </c>
@@ -1927,8 +1951,14 @@
       <c r="D3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>330</v>
       </c>
@@ -1941,8 +1971,14 @@
       <c r="D4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>331</v>
       </c>
@@ -1955,8 +1991,14 @@
       <c r="D5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>332</v>
       </c>
@@ -1969,8 +2011,14 @@
       <c r="D6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>333</v>
       </c>
@@ -1983,8 +2031,14 @@
       <c r="D7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>334</v>
       </c>
@@ -1997,8 +2051,14 @@
       <c r="D8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>335</v>
       </c>
@@ -2011,8 +2071,11 @@
       <c r="D9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="F9" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>336</v>
       </c>
@@ -2025,8 +2088,11 @@
       <c r="D10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="F10" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>337</v>
       </c>
@@ -2039,8 +2105,11 @@
       <c r="D11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="F11" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>338</v>
       </c>
@@ -2053,8 +2122,11 @@
       <c r="D12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="F12" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>339</v>
       </c>
@@ -2067,8 +2139,11 @@
       <c r="D13" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="F13" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>340</v>
       </c>
@@ -2081,8 +2156,11 @@
       <c r="D14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="F14" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>341</v>
       </c>
@@ -2095,8 +2173,11 @@
       <c r="D15" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="F15" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>342</v>
       </c>
@@ -2109,8 +2190,11 @@
       <c r="D16" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="F16" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>343</v>
       </c>
@@ -2123,8 +2207,11 @@
       <c r="D17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="F17" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>344</v>
       </c>
@@ -2137,8 +2224,11 @@
       <c r="D18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="F18" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>345</v>
       </c>
@@ -2151,8 +2241,11 @@
       <c r="D19" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="F19" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>346</v>
       </c>
@@ -2165,8 +2258,11 @@
       <c r="D20" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="F20" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>347</v>
       </c>
@@ -2179,8 +2275,11 @@
       <c r="D21" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="F21" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>348</v>
       </c>
@@ -2193,8 +2292,11 @@
       <c r="D22" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="F22" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>349</v>
       </c>
@@ -2207,8 +2309,11 @@
       <c r="D23" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="F23" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>350</v>
       </c>
@@ -2221,8 +2326,11 @@
       <c r="D24" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="F24" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>351</v>
       </c>
@@ -2235,8 +2343,11 @@
       <c r="D25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="F25" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>352</v>
       </c>
@@ -2249,8 +2360,11 @@
       <c r="D26" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="F26" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>353</v>
       </c>
@@ -2263,8 +2377,11 @@
       <c r="D27" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="F27" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>354</v>
       </c>
@@ -2277,8 +2394,11 @@
       <c r="D28" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="F28" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>355</v>
       </c>
@@ -2291,8 +2411,11 @@
       <c r="D29" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="F29" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>356</v>
       </c>
@@ -2305,8 +2428,14 @@
       <c r="D30" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>357</v>
       </c>
@@ -2319,8 +2448,14 @@
       <c r="D31" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>358</v>
       </c>
@@ -2333,8 +2468,14 @@
       <c r="D32" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>359</v>
       </c>
@@ -2347,8 +2488,14 @@
       <c r="D33" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>360</v>
       </c>
@@ -2361,8 +2508,14 @@
       <c r="D34" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>361</v>
       </c>
@@ -2375,8 +2528,14 @@
       <c r="D35" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>362</v>
       </c>
@@ -2389,8 +2548,11 @@
       <c r="D36" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="F36" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>363</v>
       </c>
@@ -2403,8 +2565,14 @@
       <c r="D37" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>364</v>
       </c>
@@ -2417,8 +2585,14 @@
       <c r="D38" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>365</v>
       </c>
@@ -2431,8 +2605,14 @@
       <c r="D39" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>366</v>
       </c>
@@ -2445,8 +2625,14 @@
       <c r="D40" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>367</v>
       </c>
@@ -2459,8 +2645,11 @@
       <c r="D41" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="F41" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>368</v>
       </c>
@@ -2473,8 +2662,11 @@
       <c r="D42" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="F42" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>369</v>
       </c>
@@ -2487,8 +2679,11 @@
       <c r="D43" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="F43" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>370</v>
       </c>
@@ -2501,8 +2696,14 @@
       <c r="D44" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>371</v>
       </c>
@@ -2515,8 +2716,14 @@
       <c r="D45" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>372</v>
       </c>
@@ -2529,8 +2736,14 @@
       <c r="D46" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>373</v>
       </c>
@@ -2543,8 +2756,11 @@
       <c r="D47" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="F47" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>374</v>
       </c>
@@ -2557,8 +2773,11 @@
       <c r="D48" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="F48" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>375</v>
       </c>
@@ -2571,8 +2790,11 @@
       <c r="D49" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="F49" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>376</v>
       </c>
@@ -2585,8 +2807,11 @@
       <c r="D50" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="F50" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>377</v>
       </c>
@@ -2599,8 +2824,14 @@
       <c r="D51" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>378</v>
       </c>
@@ -2613,8 +2844,14 @@
       <c r="D52" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>379</v>
       </c>
@@ -2627,8 +2864,14 @@
       <c r="D53" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>380</v>
       </c>
@@ -2641,8 +2884,14 @@
       <c r="D54" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>381</v>
       </c>
@@ -2655,8 +2904,14 @@
       <c r="D55" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>382</v>
       </c>
@@ -2669,8 +2924,11 @@
       <c r="D56" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="F56" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>383</v>
       </c>
@@ -2683,8 +2941,11 @@
       <c r="D57" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="F57" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>384</v>
       </c>
@@ -2697,8 +2958,11 @@
       <c r="D58" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="F58" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>385</v>
       </c>
@@ -2711,8 +2975,11 @@
       <c r="D59" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="F59" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>386</v>
       </c>
@@ -2725,8 +2992,11 @@
       <c r="D60" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="F60" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>387</v>
       </c>
@@ -2739,8 +3009,11 @@
       <c r="D61" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="F61" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>388</v>
       </c>
@@ -2753,8 +3026,14 @@
       <c r="D62" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>389</v>
       </c>
@@ -2767,8 +3046,11 @@
       <c r="D63" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="F63" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>390</v>
       </c>
@@ -2781,8 +3063,11 @@
       <c r="D64" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="F64" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>391</v>
       </c>
@@ -2795,8 +3080,11 @@
       <c r="D65" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="F65" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>392</v>
       </c>
@@ -2809,8 +3097,11 @@
       <c r="D66" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="F66" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>393</v>
       </c>
@@ -2823,8 +3114,11 @@
       <c r="D67" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="F67" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>394</v>
       </c>
@@ -2837,8 +3131,11 @@
       <c r="D68" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="F68" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>395</v>
       </c>
@@ -2851,8 +3148,14 @@
       <c r="D69" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>396</v>
       </c>
@@ -2865,8 +3168,14 @@
       <c r="D70" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>397</v>
       </c>
@@ -2879,8 +3188,14 @@
       <c r="D71" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>398</v>
       </c>
@@ -2893,8 +3208,11 @@
       <c r="D72" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="F72" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>399</v>
       </c>
@@ -2907,8 +3225,11 @@
       <c r="D73" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="F73" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>400</v>
       </c>
@@ -2921,8 +3242,11 @@
       <c r="D74" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="F74" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>401</v>
       </c>
@@ -2935,8 +3259,14 @@
       <c r="D75" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="E75" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>402</v>
       </c>
@@ -2949,8 +3279,11 @@
       <c r="D76" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="F76" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>403</v>
       </c>
@@ -2963,8 +3296,14 @@
       <c r="D77" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="E77" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>404</v>
       </c>
@@ -2977,8 +3316,14 @@
       <c r="D78" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>405</v>
       </c>
@@ -2991,8 +3336,14 @@
       <c r="D79" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="E79" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>406</v>
       </c>
@@ -3005,8 +3356,14 @@
       <c r="D80" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>407</v>
       </c>
@@ -3019,8 +3376,14 @@
       <c r="D81" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>408</v>
       </c>
@@ -3033,8 +3396,11 @@
       <c r="D82" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="F82" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>409</v>
       </c>
@@ -3047,8 +3413,14 @@
       <c r="D83" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
+      <c r="E83" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>410</v>
       </c>
@@ -3061,8 +3433,14 @@
       <c r="D84" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="85" spans="1:4">
+      <c r="E84" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>411</v>
       </c>
@@ -3075,8 +3453,14 @@
       <c r="D85" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="E85" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>412</v>
       </c>
@@ -3089,8 +3473,14 @@
       <c r="D86" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="E86" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>413</v>
       </c>
@@ -3103,8 +3493,14 @@
       <c r="D87" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="E87" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>414</v>
       </c>
@@ -3117,8 +3513,11 @@
       <c r="D88" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="89" spans="1:4">
+      <c r="F88" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>415</v>
       </c>
@@ -3131,8 +3530,11 @@
       <c r="D89" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
+      <c r="F89" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>416</v>
       </c>
@@ -3145,8 +3547,14 @@
       <c r="D90" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="E90" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>417</v>
       </c>
@@ -3159,8 +3567,11 @@
       <c r="D91" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="92" spans="1:4">
+      <c r="F91" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>418</v>
       </c>
@@ -3173,8 +3584,11 @@
       <c r="D92" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="93" spans="1:4">
+      <c r="F92" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>419</v>
       </c>
@@ -3187,8 +3601,14 @@
       <c r="D93" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="94" spans="1:4">
+      <c r="E93" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>420</v>
       </c>
@@ -3201,8 +3621,11 @@
       <c r="D94" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="95" spans="1:4">
+      <c r="F94" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>421</v>
       </c>
@@ -3215,8 +3638,14 @@
       <c r="D95" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="96" spans="1:4">
+      <c r="E95" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>422</v>
       </c>
@@ -3229,8 +3658,14 @@
       <c r="D96" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="97" spans="1:4">
+      <c r="E96" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>423</v>
       </c>
@@ -3243,8 +3678,14 @@
       <c r="D97" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="98" spans="1:4">
+      <c r="E97" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>424</v>
       </c>
@@ -3257,8 +3698,11 @@
       <c r="D98" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="99" spans="1:4">
+      <c r="F98" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>425</v>
       </c>
@@ -3271,8 +3715,11 @@
       <c r="D99" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="100" spans="1:4">
+      <c r="F99" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>426</v>
       </c>
@@ -3285,8 +3732,14 @@
       <c r="D100" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="101" spans="1:4">
+      <c r="E100" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>427</v>
       </c>
@@ -3299,8 +3752,14 @@
       <c r="D101" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="102" spans="1:4">
+      <c r="E101" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>428</v>
       </c>
@@ -3313,8 +3772,14 @@
       <c r="D102" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
+      <c r="E102" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>429</v>
       </c>
@@ -3327,8 +3792,11 @@
       <c r="D103" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="104" spans="1:4">
+      <c r="F103" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>430</v>
       </c>
@@ -3341,8 +3809,14 @@
       <c r="D104" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
+      <c r="E104" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>431</v>
       </c>
@@ -3355,8 +3829,14 @@
       <c r="D105" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="106" spans="1:4">
+      <c r="E105" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>432</v>
       </c>
@@ -3369,8 +3849,14 @@
       <c r="D106" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="107" spans="1:4">
+      <c r="E106" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>433</v>
       </c>
@@ -3383,8 +3869,14 @@
       <c r="D107" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
+      <c r="E107" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>434</v>
       </c>
@@ -3397,8 +3889,14 @@
       <c r="D108" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="109" spans="1:4">
+      <c r="E108" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>435</v>
       </c>
@@ -3411,8 +3909,14 @@
       <c r="D109" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
+      <c r="E109" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>436</v>
       </c>
@@ -3425,8 +3929,11 @@
       <c r="D110" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="111" spans="1:4">
+      <c r="F110" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>437</v>
       </c>
@@ -3439,8 +3946,11 @@
       <c r="D111" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
+      <c r="F111" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>438</v>
       </c>
@@ -3453,8 +3963,11 @@
       <c r="D112" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="113" spans="1:4">
+      <c r="F112" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>439</v>
       </c>
@@ -3467,8 +3980,11 @@
       <c r="D113" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="114" spans="1:4">
+      <c r="F113" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>440</v>
       </c>
@@ -3481,8 +3997,11 @@
       <c r="D114" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="115" spans="1:4">
+      <c r="F114" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>441</v>
       </c>
@@ -3495,8 +4014,14 @@
       <c r="D115" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="116" spans="1:4">
+      <c r="E115" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>442</v>
       </c>
@@ -3509,8 +4034,11 @@
       <c r="D116" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="117" spans="1:4">
+      <c r="F116" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>443</v>
       </c>
@@ -3523,8 +4051,11 @@
       <c r="D117" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="118" spans="1:4">
+      <c r="F117" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>444</v>
       </c>
@@ -3537,8 +4068,11 @@
       <c r="D118" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="119" spans="1:4">
+      <c r="F118" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>445</v>
       </c>
@@ -3551,8 +4085,14 @@
       <c r="D119" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="120" spans="1:4">
+      <c r="E119" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>446</v>
       </c>
@@ -3565,8 +4105,14 @@
       <c r="D120" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="121" spans="1:4">
+      <c r="E120" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>447</v>
       </c>
@@ -3579,8 +4125,11 @@
       <c r="D121" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="122" spans="1:4">
+      <c r="F121" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>448</v>
       </c>
@@ -3593,8 +4142,14 @@
       <c r="D122" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="123" spans="1:4">
+      <c r="E122" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>449</v>
       </c>
@@ -3607,8 +4162,11 @@
       <c r="D123" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="124" spans="1:4">
+      <c r="F123" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>450</v>
       </c>
@@ -3621,8 +4179,14 @@
       <c r="D124" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="125" spans="1:4">
+      <c r="E124" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>451</v>
       </c>
@@ -3635,8 +4199,14 @@
       <c r="D125" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="126" spans="1:4">
+      <c r="E125" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>452</v>
       </c>
@@ -3649,8 +4219,14 @@
       <c r="D126" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="127" spans="1:4">
+      <c r="E126" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>453</v>
       </c>
@@ -3663,8 +4239,14 @@
       <c r="D127" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="128" spans="1:4">
+      <c r="E127" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>454</v>
       </c>
@@ -3677,8 +4259,14 @@
       <c r="D128" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="129" spans="1:4">
+      <c r="E128" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>455</v>
       </c>
@@ -3691,8 +4279,14 @@
       <c r="D129" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="130" spans="1:4">
+      <c r="E129" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>456</v>
       </c>
@@ -3705,8 +4299,14 @@
       <c r="D130" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="131" spans="1:4">
+      <c r="E130" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>457</v>
       </c>
@@ -3719,8 +4319,14 @@
       <c r="D131" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="132" spans="1:4">
+      <c r="E131" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>458</v>
       </c>
@@ -3733,8 +4339,14 @@
       <c r="D132" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="133" spans="1:4">
+      <c r="E132" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>459</v>
       </c>
@@ -3747,8 +4359,14 @@
       <c r="D133" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="134" spans="1:4">
+      <c r="E133" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>460</v>
       </c>
@@ -3761,8 +4379,11 @@
       <c r="D134" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="135" spans="1:4">
+      <c r="F134" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>461</v>
       </c>
@@ -3775,8 +4396,11 @@
       <c r="D135" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="136" spans="1:4">
+      <c r="F135" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>462</v>
       </c>
@@ -3789,8 +4413,11 @@
       <c r="D136" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="137" spans="1:4">
+      <c r="F136" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>463</v>
       </c>
@@ -3803,8 +4430,14 @@
       <c r="D137" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="138" spans="1:4">
+      <c r="E137" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>464</v>
       </c>
@@ -3817,8 +4450,14 @@
       <c r="D138" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="139" spans="1:4">
+      <c r="E138" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>465</v>
       </c>
@@ -3831,8 +4470,11 @@
       <c r="D139" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="140" spans="1:4">
+      <c r="F139" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>466</v>
       </c>
@@ -3845,8 +4487,11 @@
       <c r="D140" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="141" spans="1:4">
+      <c r="F140" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>467</v>
       </c>
@@ -3859,8 +4504,11 @@
       <c r="D141" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="142" spans="1:4">
+      <c r="F141" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>468</v>
       </c>
@@ -3873,8 +4521,11 @@
       <c r="D142" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="143" spans="1:4">
+      <c r="F142" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>469</v>
       </c>
@@ -3887,8 +4538,14 @@
       <c r="D143" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="144" spans="1:4">
+      <c r="E143" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>470</v>
       </c>
@@ -3901,8 +4558,11 @@
       <c r="D144" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="145" spans="1:4">
+      <c r="F144" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>471</v>
       </c>
@@ -3915,8 +4575,14 @@
       <c r="D145" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="146" spans="1:4">
+      <c r="E145" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>472</v>
       </c>
@@ -3929,8 +4595,14 @@
       <c r="D146" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="147" spans="1:4">
+      <c r="E146" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>473</v>
       </c>
@@ -3943,8 +4615,11 @@
       <c r="D147" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="148" spans="1:4">
+      <c r="F147" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>474</v>
       </c>
@@ -3957,8 +4632,11 @@
       <c r="D148" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="149" spans="1:4">
+      <c r="F148" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>475</v>
       </c>
@@ -3971,8 +4649,11 @@
       <c r="D149" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="150" spans="1:4">
+      <c r="F149" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>476</v>
       </c>
@@ -3985,8 +4666,11 @@
       <c r="D150" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="151" spans="1:4">
+      <c r="F150" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>477</v>
       </c>
@@ -3999,8 +4683,11 @@
       <c r="D151" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="152" spans="1:4">
+      <c r="F151" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>478</v>
       </c>
@@ -4013,8 +4700,14 @@
       <c r="D152" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="153" spans="1:4">
+      <c r="E152" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>479</v>
       </c>
@@ -4026,6 +4719,9 @@
       </c>
       <c r="D153" t="s">
         <v>304</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -4036,10 +4732,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <WS_KM xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">false</WS_KM>
@@ -4059,13 +4751,12 @@
 </p:properties>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"excel-template-wavestone","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4381,16 +5072,15 @@
 </file>
 
 <file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"excel-template-wavestone","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BA3DF0-87BD-4820-849B-A09A7499F975}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD40D982-8286-4B8F-A856-9520176C5B63}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -4408,11 +5098,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BA3DF0-87BD-4820-849B-A09A7499F975}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60AEAD36-3C40-43A4-8069-DD963241733E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6833886D-AFD0-4394-A643-4CABE4FE0F96}">
+  <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
@@ -4437,7 +5131,9 @@
 </file>
 
 <file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6833886D-AFD0-4394-A643-4CABE4FE0F96}">
-  <ds:schemaRefs/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60AEAD36-3C40-43A4-8069-DD963241733E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
 </ds:datastoreItem>
 </file>